--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/GEORGIA_2014.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/GEORGIA_2014.xlsx
@@ -985,7 +985,7 @@
         <v>24</v>
       </c>
       <c r="D35">
-        <v>0.000926068837784</v>
+        <v>0.0009260688377840002</v>
       </c>
     </row>
     <row r="36">
@@ -1183,7 +1183,7 @@
         <v>24</v>
       </c>
       <c r="D46">
-        <v>0.000926068837784</v>
+        <v>0.0009260688377840002</v>
       </c>
     </row>
     <row r="47">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C129">
@@ -4405,7 +4405,7 @@
         <v>24</v>
       </c>
       <c r="D225">
-        <v>0.000926068837784</v>
+        <v>0.0009260688377840002</v>
       </c>
     </row>
     <row r="226">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C304">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C314">
@@ -8689,7 +8689,7 @@
         <v>24</v>
       </c>
       <c r="D463">
-        <v>0.000926068837784</v>
+        <v>0.0009260688377840002</v>
       </c>
     </row>
     <row r="464">
@@ -12181,7 +12181,7 @@
         <v>24</v>
       </c>
       <c r="D657">
-        <v>0.000926068837784</v>
+        <v>0.0009260688377840002</v>
       </c>
     </row>
     <row r="658">
@@ -13956,7 +13956,7 @@
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C756">
@@ -14071,7 +14071,7 @@
         <v>24</v>
       </c>
       <c r="D762">
-        <v>0.000926068837784</v>
+        <v>0.0009260688377840002</v>
       </c>
     </row>
     <row r="763">
@@ -15828,7 +15828,7 @@
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C860">
@@ -15846,7 +15846,7 @@
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C861">
@@ -16692,7 +16692,7 @@
       </c>
       <c r="B908" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C908">
@@ -18366,7 +18366,7 @@
       </c>
       <c r="B1001" t="inlineStr">
         <is>
-          <t>Santo Domingo Tonaltepec</t>
+          <t>Santo Domingo Tomaltepec</t>
         </is>
       </c>
       <c r="C1001">
@@ -22675,7 +22675,7 @@
         <v>24</v>
       </c>
       <c r="D1240">
-        <v>0.000926068837784</v>
+        <v>0.0009260688377840002</v>
       </c>
     </row>
     <row r="1241">
@@ -26815,7 +26815,7 @@
         <v>24</v>
       </c>
       <c r="D1470">
-        <v>0.000926068837784</v>
+        <v>0.0009260688377840002</v>
       </c>
     </row>
     <row r="1471">
@@ -27204,7 +27204,7 @@
       </c>
       <c r="B1492" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1492">
